--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/LOUISIANA_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/LOUISIANA_2016.xlsx
@@ -463,7 +463,7 @@
         <v>3</v>
       </c>
       <c r="D6">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="7">
@@ -589,7 +589,7 @@
         <v>3</v>
       </c>
       <c r="D13">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="14">
@@ -751,7 +751,7 @@
         <v>3</v>
       </c>
       <c r="D22">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="23">
@@ -841,7 +841,7 @@
         <v>3</v>
       </c>
       <c r="D27">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="28">
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="D31">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="32">
@@ -1003,7 +1003,7 @@
         <v>3</v>
       </c>
       <c r="D36">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="37">
@@ -1057,7 +1057,7 @@
         <v>3</v>
       </c>
       <c r="D39">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="40">
@@ -1183,7 +1183,7 @@
         <v>3</v>
       </c>
       <c r="D46">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="47">
@@ -1381,7 +1381,7 @@
         <v>3</v>
       </c>
       <c r="D57">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="58">
@@ -1633,7 +1633,7 @@
         <v>3</v>
       </c>
       <c r="D71">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="72">
@@ -1687,7 +1687,7 @@
         <v>3</v>
       </c>
       <c r="D74">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="75">
@@ -1741,7 +1741,7 @@
         <v>3</v>
       </c>
       <c r="D77">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="78">
@@ -2083,7 +2083,7 @@
         <v>3</v>
       </c>
       <c r="D96">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="97">
@@ -2101,7 +2101,7 @@
         <v>3</v>
       </c>
       <c r="D97">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="98">
@@ -2515,7 +2515,7 @@
         <v>3</v>
       </c>
       <c r="D120">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="121">
@@ -2551,7 +2551,7 @@
         <v>3</v>
       </c>
       <c r="D122">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="123">
@@ -2587,7 +2587,7 @@
         <v>3</v>
       </c>
       <c r="D124">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="125">
@@ -2677,7 +2677,7 @@
         <v>3</v>
       </c>
       <c r="D129">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="130">
@@ -2911,7 +2911,7 @@
         <v>3</v>
       </c>
       <c r="D142">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="143">
@@ -3523,7 +3523,7 @@
         <v>3</v>
       </c>
       <c r="D176">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="177">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C178">
@@ -3577,7 +3577,7 @@
         <v>3</v>
       </c>
       <c r="D179">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="180">
@@ -3883,7 +3883,7 @@
         <v>3</v>
       </c>
       <c r="D196">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="197">
@@ -3901,7 +3901,7 @@
         <v>3</v>
       </c>
       <c r="D197">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="198">
@@ -4063,7 +4063,7 @@
         <v>3</v>
       </c>
       <c r="D206">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="207">
@@ -4351,7 +4351,7 @@
         <v>3</v>
       </c>
       <c r="D222">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="223">
@@ -4423,7 +4423,7 @@
         <v>3</v>
       </c>
       <c r="D226">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="227">
@@ -4495,7 +4495,7 @@
         <v>3</v>
       </c>
       <c r="D230">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="231">
@@ -4549,7 +4549,7 @@
         <v>3</v>
       </c>
       <c r="D233">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="234">
@@ -4603,7 +4603,7 @@
         <v>3</v>
       </c>
       <c r="D236">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="237">
@@ -4693,7 +4693,7 @@
         <v>3</v>
       </c>
       <c r="D241">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="242">
@@ -4837,7 +4837,7 @@
         <v>3</v>
       </c>
       <c r="D249">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="250">
@@ -4927,7 +4927,7 @@
         <v>3</v>
       </c>
       <c r="D254">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="255">
@@ -5143,7 +5143,7 @@
         <v>3</v>
       </c>
       <c r="D266">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="267">
@@ -5701,7 +5701,7 @@
         <v>3</v>
       </c>
       <c r="D297">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="298">
@@ -5809,7 +5809,7 @@
         <v>3</v>
       </c>
       <c r="D303">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="304">
@@ -6313,7 +6313,7 @@
         <v>3</v>
       </c>
       <c r="D331">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="332">
@@ -6349,7 +6349,7 @@
         <v>3</v>
       </c>
       <c r="D333">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="334">
@@ -6403,7 +6403,7 @@
         <v>3</v>
       </c>
       <c r="D336">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="337">
@@ -6529,7 +6529,7 @@
         <v>3</v>
       </c>
       <c r="D343">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="344">
@@ -6637,7 +6637,7 @@
         <v>3</v>
       </c>
       <c r="D349">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="350">
@@ -6691,7 +6691,7 @@
         <v>3</v>
       </c>
       <c r="D352">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="353">
@@ -7069,7 +7069,7 @@
         <v>3</v>
       </c>
       <c r="D373">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="374">
@@ -7123,7 +7123,7 @@
         <v>3</v>
       </c>
       <c r="D376">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="377">
@@ -7249,7 +7249,7 @@
         <v>3</v>
       </c>
       <c r="D383">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="384">
@@ -7357,7 +7357,7 @@
         <v>3</v>
       </c>
       <c r="D389">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="390">
@@ -7699,7 +7699,7 @@
         <v>3</v>
       </c>
       <c r="D408">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="409">
@@ -7753,7 +7753,7 @@
         <v>3</v>
       </c>
       <c r="D411">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="412">
@@ -7771,7 +7771,7 @@
         <v>3</v>
       </c>
       <c r="D412">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="413">
@@ -8023,7 +8023,7 @@
         <v>3</v>
       </c>
       <c r="D426">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="427">
@@ -8239,7 +8239,7 @@
         <v>3</v>
       </c>
       <c r="D438">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="439">
@@ -8635,7 +8635,7 @@
         <v>3</v>
       </c>
       <c r="D460">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="461">
@@ -8851,7 +8851,7 @@
         <v>3</v>
       </c>
       <c r="D472">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="473">
@@ -9013,7 +9013,7 @@
         <v>3</v>
       </c>
       <c r="D481">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="482">
@@ -9121,7 +9121,7 @@
         <v>3</v>
       </c>
       <c r="D487">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="488">
@@ -9139,7 +9139,7 @@
         <v>3</v>
       </c>
       <c r="D488">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="489">
@@ -9157,7 +9157,7 @@
         <v>32</v>
       </c>
       <c r="D489">
-        <v>0.009679370840895343</v>
+        <v>0.009679370840895344</v>
       </c>
     </row>
     <row r="490">
@@ -9211,7 +9211,7 @@
         <v>3</v>
       </c>
       <c r="D492">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="493">
@@ -9265,7 +9265,7 @@
         <v>3</v>
       </c>
       <c r="D495">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="496">
@@ -9463,7 +9463,7 @@
         <v>3</v>
       </c>
       <c r="D506">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="507">
@@ -9697,7 +9697,7 @@
         <v>33</v>
       </c>
       <c r="D519">
-        <v>0.009981851179673321</v>
+        <v>0.00998185117967332</v>
       </c>
     </row>
     <row r="520">
@@ -10381,7 +10381,7 @@
         <v>3</v>
       </c>
       <c r="D557">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="558">
@@ -10399,7 +10399,7 @@
         <v>3</v>
       </c>
       <c r="D558">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="559">
@@ -10507,7 +10507,7 @@
         <v>3</v>
       </c>
       <c r="D564">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="565">
@@ -10525,7 +10525,7 @@
         <v>32</v>
       </c>
       <c r="D565">
-        <v>0.009679370840895343</v>
+        <v>0.009679370840895344</v>
       </c>
     </row>
     <row r="566">
@@ -10651,7 +10651,7 @@
         <v>3</v>
       </c>
       <c r="D572">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="573">
@@ -10705,7 +10705,7 @@
         <v>3</v>
       </c>
       <c r="D575">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="576">
@@ -10723,7 +10723,7 @@
         <v>3</v>
       </c>
       <c r="D576">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="577">
@@ -10813,7 +10813,7 @@
         <v>3</v>
       </c>
       <c r="D581">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="582">
@@ -11083,7 +11083,7 @@
         <v>3</v>
       </c>
       <c r="D596">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="597">
@@ -11173,7 +11173,7 @@
         <v>3</v>
       </c>
       <c r="D601">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="602">
@@ -11353,7 +11353,7 @@
         <v>3</v>
       </c>
       <c r="D611">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="612">
@@ -11605,7 +11605,7 @@
         <v>3</v>
       </c>
       <c r="D625">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="626">
@@ -11677,7 +11677,7 @@
         <v>32</v>
       </c>
       <c r="D629">
-        <v>0.009679370840895343</v>
+        <v>0.009679370840895344</v>
       </c>
     </row>
     <row r="630">
@@ -11821,7 +11821,7 @@
         <v>3</v>
       </c>
       <c r="D637">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="638">
@@ -11875,7 +11875,7 @@
         <v>3</v>
       </c>
       <c r="D640">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="641">
@@ -12055,7 +12055,7 @@
         <v>3</v>
       </c>
       <c r="D650">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="651">
@@ -12217,7 +12217,7 @@
         <v>3</v>
       </c>
       <c r="D659">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="660">
@@ -12415,7 +12415,7 @@
         <v>3</v>
       </c>
       <c r="D670">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="671">
@@ -12541,7 +12541,7 @@
         <v>3</v>
       </c>
       <c r="D677">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="678">
@@ -12577,7 +12577,7 @@
         <v>3</v>
       </c>
       <c r="D679">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="680">
@@ -12703,7 +12703,7 @@
         <v>3</v>
       </c>
       <c r="D686">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="687">
@@ -13207,7 +13207,7 @@
         <v>3</v>
       </c>
       <c r="D714">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="715">
@@ -13243,7 +13243,7 @@
         <v>3</v>
       </c>
       <c r="D716">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="717">
@@ -13297,7 +13297,7 @@
         <v>3</v>
       </c>
       <c r="D719">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="720">
@@ -13315,7 +13315,7 @@
         <v>3</v>
       </c>
       <c r="D720">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="721">
@@ -13657,7 +13657,7 @@
         <v>3</v>
       </c>
       <c r="D739">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="740">
@@ -13945,7 +13945,7 @@
         <v>3</v>
       </c>
       <c r="D755">
-        <v>0.0009074410163339383</v>
+        <v>0.0009074410163339384</v>
       </c>
     </row>
     <row r="756">
